--- a/hema/0-HeMa/3-单袋比.xlsx
+++ b/hema/0-HeMa/3-单袋比.xlsx
@@ -1871,7 +1871,7 @@
     <row r="1" spans="1:12">
       <c r="A1" s="41">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46134</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
@@ -7195,7 +7195,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="19" cm="1">
-        <f t="array" ref="C2:C300">SUMIFS(配送员履约明细表!W2:W5000,配送员履约明细表!J2:J5000,A2:A300)</f>
+        <f t="array" ref="C2:C300">SUMIFS(配送员履约明细表!AQ2:AQ5000,配送员履约明细表!J2:J5000,A2:A300)</f>
         <v>0</v>
       </c>
       <c r="D2" s="15" t="str" cm="1">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="R2" s="21">
         <f ca="1">TODAY()</f>
-        <v>46120</v>
+        <v>46134</v>
       </c>
       <c r="S2" s="19"/>
       <c r="T2" s="19"/>
